--- a/data/trans_dic/P16A_2_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,14; 22,29</t>
+          <t>14,8; 22,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,77; 35,37</t>
+          <t>27,4; 35,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 27,07</t>
+          <t>21,84; 27,13</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 24,31</t>
+          <t>16,7; 24,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,87; 35,75</t>
+          <t>27,95; 36,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,89; 28,62</t>
+          <t>23,08; 28,47</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 28,43</t>
+          <t>6,87; 28,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,17; 52,76</t>
+          <t>40,38; 52,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 33,67</t>
+          <t>10,8; 33,47</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 31,45</t>
+          <t>25,49; 31,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,7; 74,44</t>
+          <t>37,45; 71,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,99; 56,46</t>
+          <t>32,0; 59,23</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,62; 31,07</t>
+          <t>23,13; 31,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,13; 49,0</t>
+          <t>32,8; 49,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,11; 40,99</t>
+          <t>30,46; 40,82</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,14; 23,47</t>
+          <t>7,38; 23,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,22; 41,38</t>
+          <t>35,31; 41,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,04; 35,32</t>
+          <t>29,4; 35,43</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,1; 24,64</t>
+          <t>17,61; 24,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,56; 53,35</t>
+          <t>37,41; 52,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,0; 38,58</t>
+          <t>29,03; 39,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76498; 112633</t>
+          <t>74783; 113420</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>124277; 158259</t>
+          <t>122590; 156674</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>209912; 257927</t>
+          <t>208026; 258487</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75631; 109937</t>
+          <t>75538; 110341</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106634; 136761</t>
+          <t>106927; 138636</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>191092; 238927</t>
+          <t>192666; 237681</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41494; 190014</t>
+          <t>45919; 190821</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67042; 88057</t>
+          <t>67395; 88083</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83564; 281209</t>
+          <t>90192; 279501</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>265498; 325473</t>
+          <t>263797; 325947</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>368704; 728118</t>
+          <t>366251; 694402</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>643868; 1136447</t>
+          <t>644084; 1192176</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>107443; 147592</t>
+          <t>109868; 150155</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>261935; 412256</t>
+          <t>275964; 414067</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>409510; 539589</t>
+          <t>400928; 537376</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>291760</t>
+          <t>291759</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17169; 56444</t>
+          <t>17749; 55648</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268138; 315035</t>
+          <t>268873; 316705</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>290979; 353816</t>
+          <t>294509; 354941</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>577363; 831716</t>
+          <t>594542; 833426</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1343811; 1908621</t>
+          <t>1338469; 1894866</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2016631; 2682823</t>
+          <t>2018354; 2733136</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_2_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,8; 22,45</t>
+          <t>15,88; 22,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,4; 35,01</t>
+          <t>26,87; 33,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,84; 27,13</t>
+          <t>21,91; 26,79</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 24,4</t>
+          <t>16,08; 23,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,95; 36,24</t>
+          <t>27,8; 35,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 28,47</t>
+          <t>22,57; 27,91</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 28,55</t>
+          <t>22,83; 31,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,38; 52,77</t>
+          <t>39,61; 52,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 33,47</t>
+          <t>29,09; 36,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,49; 31,5</t>
+          <t>25,19; 30,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,45; 71,0</t>
+          <t>35,65; 41,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,0; 59,23</t>
+          <t>30,63; 34,75</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,13; 31,61</t>
+          <t>21,4; 29,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,8; 49,22</t>
+          <t>44,56; 50,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,46; 40,82</t>
+          <t>36,0; 41,01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 23,14</t>
+          <t>5,98; 18,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,31; 41,6</t>
+          <t>34,58; 40,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,4; 35,43</t>
+          <t>28,66; 34,42</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,61; 24,69</t>
+          <t>22,09; 25,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,41; 52,96</t>
+          <t>37,41; 40,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,03; 39,3</t>
+          <t>30,33; 32,5</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92173</t>
+          <t>105516</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>139976</t>
+          <t>148784</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232149</t>
+          <t>254300</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74783; 113420</t>
+          <t>87444; 126029</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122590; 156674</t>
+          <t>131213; 165200</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>208026; 258487</t>
+          <t>227618; 278349</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>92503</t>
+          <t>94294</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>122005</t>
+          <t>133481</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214508</t>
+          <t>227775</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75538; 110341</t>
+          <t>77677; 112405</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106927; 138636</t>
+          <t>117615; 151172</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>192666; 237681</t>
+          <t>204519; 252996</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>115017</t>
+          <t>127926</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>85711</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192373</t>
+          <t>213637</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45919; 190821</t>
+          <t>107657; 148222</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67395; 88083</t>
+          <t>74266; 98023</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90192; 279501</t>
+          <t>191753; 237283</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>294198</t>
+          <t>316250</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>502874</t>
+          <t>332732</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>797072</t>
+          <t>648982</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>263797; 325947</t>
+          <t>285102; 347857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>366251; 694402</t>
+          <t>307052; 356146</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>644084; 1192176</t>
+          <t>610445; 692686</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>128160</t>
+          <t>142753</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>361792</t>
+          <t>394012</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489952</t>
+          <t>536765</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>109868; 150155</t>
+          <t>121563; 166336</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>275964; 414067</t>
+          <t>370233; 418546</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>400928; 537376</t>
+          <t>503635; 573590</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>31244</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>291759</t>
+          <t>314728</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323004</t>
+          <t>341061</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17749; 55648</t>
+          <t>14183; 44130</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268873; 316705</t>
+          <t>291968; 340804</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>294509; 354941</t>
+          <t>309985; 372299</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>753296</t>
+          <t>813071</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1495762</t>
+          <t>1409448</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2249057</t>
+          <t>2222519</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>594542; 833426</t>
+          <t>760532; 866164</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1338469; 1894866</t>
+          <t>1360056; 1460974</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2018354; 2733136</t>
+          <t>2146457; 2300088</t>
         </is>
       </c>
     </row>
